--- a/test-data/page-title-data.xlsx
+++ b/test-data/page-title-data.xlsx
@@ -1,36 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10123"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/learnb/git/digiplat-qa/test-data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geopopkh/eclipse-workspace/cgov-digital-platform-qa/test-data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741314E5-CFFF-224A-AE2B-D6D6FFAB2E08}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC44B751-1537-1A4A-A8F9-853ECFCEBD71}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25700" yWindow="4380" windowWidth="27640" windowHeight="16940" xr2:uid="{112BCE41-1B7B-AF44-BEF2-07A92CFC037C}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="15940" xr2:uid="{112BCE41-1B7B-AF44-BEF2-07A92CFC037C}"/>
   </bookViews>
   <sheets>
     <sheet name="browser_and_page_titles" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>path</t>
   </si>
@@ -50,21 +46,9 @@
     <t>English</t>
   </si>
   <si>
-    <t>/espanol/node/1</t>
-  </si>
-  <si>
     <t>Spanish</t>
   </si>
   <si>
-    <t>/about-cancer/coping/feelings/relaxation</t>
-  </si>
-  <si>
-    <t>/espanol/node/6</t>
-  </si>
-  <si>
-    <t>/node/36</t>
-  </si>
-  <si>
     <t>Cancer Center</t>
   </si>
   <si>
@@ -74,34 +58,115 @@
     <t>content_title</t>
   </si>
   <si>
-    <t>Feelings and Cancer | CGDP - Dev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feelings and Cancer </t>
-  </si>
-  <si>
-    <t>Los sentimientos y el cáncer | CGDP - Dev</t>
-  </si>
-  <si>
     <t>Los sentimientos y el cáncer</t>
   </si>
   <si>
-    <t>Learning to Relax | CGDP - Dev</t>
-  </si>
-  <si>
-    <t>Learning to Relax</t>
-  </si>
-  <si>
-    <t>Aprenda a relajarse | CGDP - Dev</t>
-  </si>
-  <si>
-    <t>Aprenda a relajarse</t>
-  </si>
-  <si>
-    <t>Duke Cancer Center | CGDP - Dev</t>
-  </si>
-  <si>
     <t>Duke Cancer Center</t>
+  </si>
+  <si>
+    <t>Feelings and Cancer | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Los sentimientos y el cáncer | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Blog</t>
+  </si>
+  <si>
+    <t>Press Release</t>
+  </si>
+  <si>
+    <t>Bio</t>
+  </si>
+  <si>
+    <t>about-cancer/coping/feelings/relaxation/dukeci</t>
+  </si>
+  <si>
+    <t>Jennifer K. Loukissas, M.P.P. | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Duke Cancer Center | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>espanol/noticias/comunicados-de-prensa/2018/tmds-aml-riesgo-quimio</t>
+  </si>
+  <si>
+    <t>Estudio encuentra elevado riesgo de algunos raros cánceres de la sangre después de quimioterapia para la mayoría de los tumores sólidos | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>espanol/cancer/sobrellevar/sentimientos</t>
+  </si>
+  <si>
+    <t>news-events/press-releases/2018/tmds-aml-risk-chemo</t>
+  </si>
+  <si>
+    <t>Study finds elevated risk of certain rare blood cancers after chemotherapy for most solid tumors | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>about-cancer/coping/feelings/relaxation/loukissas-jennifer</t>
+  </si>
+  <si>
+    <t>about-cancer/coping/feelings/relaxation/vitamin-d-supplement-cancer-prevention</t>
+  </si>
+  <si>
+    <t>espanol/about-cancer/coping/feelings/relaxation/vitamina-d-complemento-cancer-prevencion</t>
+  </si>
+  <si>
+    <t>Vitamin D Supplements Don’t Reduce Cancer Incidence, Trial Shows</t>
+  </si>
+  <si>
+    <t>Vitamin D Supplements Don’t Reduce Cancer Incidence, Trial Shows | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Estudio indica que complementos de vitamina D no reducen la incidencia de cáncer | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>news-events/cancer-currents-blog</t>
+  </si>
+  <si>
+    <t>Blog Series</t>
+  </si>
+  <si>
+    <t>Cancer Currents Blog</t>
+  </si>
+  <si>
+    <t>Cancer Currents Blog | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Temas y relatos blog | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Coordinating Center for Clinical Trials (CCCT)</t>
+  </si>
+  <si>
+    <t>about-nci/organization/ccct</t>
+  </si>
+  <si>
+    <t>Mini Landing Page</t>
+  </si>
+  <si>
+    <t>Coordinating Center for Clinical Trials (CCCT) | Cancer.gov Digital Platform Microsite</t>
+  </si>
+  <si>
+    <t>Feelings and Cancer</t>
+  </si>
+  <si>
+    <t>Estudio indica que complementos de vitamina D no reducen la incidencia de cáncer</t>
+  </si>
+  <si>
+    <t>Study finds elevated risk of certain rare blood cancers after chemotherapy for most solid tumors</t>
+  </si>
+  <si>
+    <t>Estudio encuentra elevado riesgo de algunos raros cánceres de la sangre después de quimioterapia para la mayoría de los tumores sólidos</t>
+  </si>
+  <si>
+    <t>espanol/noticias/temas-y-relatos-blog</t>
+  </si>
+  <si>
+    <t>Temas y relatos blog</t>
+  </si>
+  <si>
+    <t>Jennifer K. Loukissas, M.P.P</t>
   </si>
 </sst>
 </file>
@@ -137,8 +202,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,17 +527,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABDEF67-3BF3-604C-97A8-A43819B8E79D}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="47.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" customWidth="1"/>
+    <col min="3" max="3" width="9.5" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="38.1640625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
@@ -472,15 +547,15 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="D1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
@@ -489,82 +564,193 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="85" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EC512DE-0480-3348-91E2-44507591E146}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/test-data/page-title-data.xlsx
+++ b/test-data/page-title-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10123"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/learnb/git/digiplat-qa/test-data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\nci-repo\cgov-digital-platform-qa\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741314E5-CFFF-224A-AE2B-D6D6FFAB2E08}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12F3905-9A1B-459D-8034-B4AFFD7C6F6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25700" yWindow="4380" windowWidth="27640" windowHeight="16940" xr2:uid="{112BCE41-1B7B-AF44-BEF2-07A92CFC037C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24720" windowHeight="11625" xr2:uid="{112BCE41-1B7B-AF44-BEF2-07A92CFC037C}"/>
   </bookViews>
   <sheets>
     <sheet name="browser_and_page_titles" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>path</t>
   </si>
@@ -41,30 +41,18 @@
     <t>language</t>
   </si>
   <si>
-    <t>about-cancer/coping/feelings</t>
-  </si>
-  <si>
     <t>Article</t>
   </si>
   <si>
     <t>English</t>
   </si>
   <si>
-    <t>/espanol/node/1</t>
-  </si>
-  <si>
     <t>Spanish</t>
   </si>
   <si>
     <t>/about-cancer/coping/feelings/relaxation</t>
   </si>
   <si>
-    <t>/espanol/node/6</t>
-  </si>
-  <si>
-    <t>/node/36</t>
-  </si>
-  <si>
     <t>Cancer Center</t>
   </si>
   <si>
@@ -80,12 +68,6 @@
     <t xml:space="preserve">Feelings and Cancer </t>
   </si>
   <si>
-    <t>Los sentimientos y el cáncer | CGDP - Dev</t>
-  </si>
-  <si>
-    <t>Los sentimientos y el cáncer</t>
-  </si>
-  <si>
     <t>Learning to Relax | CGDP - Dev</t>
   </si>
   <si>
@@ -98,23 +80,50 @@
     <t>Aprenda a relajarse</t>
   </si>
   <si>
-    <t>Duke Cancer Center | CGDP - Dev</t>
-  </si>
-  <si>
-    <t>Duke Cancer Center</t>
+    <t>/about-cancer/coping/feelings/relaxation/dfharvard</t>
+  </si>
+  <si>
+    <t>Dana Farber/Harvard Cancer Center | CGDP - Dev</t>
+  </si>
+  <si>
+    <t>Dana Farber/Harvard Cancer Center</t>
+  </si>
+  <si>
+    <t>/about-cancer/coping/feelings/relaxation/loukissas-jennifer</t>
+  </si>
+  <si>
+    <t>Biography</t>
+  </si>
+  <si>
+    <t>Jennifer K. Loukissas, M.P.P.</t>
+  </si>
+  <si>
+    <t>Jennifer K. Loukissas, M.P.P. | CGDP - Dev</t>
+  </si>
+  <si>
+    <t>/about-cancer/coping/feelings</t>
+  </si>
+  <si>
+    <t>/espanol/cancer/sobrellevar/sentimientos/relajarse</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,8 +146,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,15 +464,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ABDEF67-3BF3-604C-97A8-A43819B8E79D}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.875" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="4" max="4" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -473,98 +483,99 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
+      <c r="D5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
         <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>